--- a/dados_trigo.xlsx
+++ b/dados_trigo.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7403566dc7686ca4/cHALLENGE lek/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7403566dc7686ca4/Dados Desafio LEK/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3E23692-0281-42D9-B383-726E5DD4C8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{E3E23692-0281-42D9-B383-726E5DD4C8D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD0A3875-180A-4E10-A211-C14E5853ADED}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{162981BA-B98B-45E1-BAF1-0E33564EB837}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="88">
   <si>
     <t>Commodity</t>
   </si>
@@ -782,13 +782,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1271,1240 +1268,1290 @@
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>1.468</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>1.7250000000000001</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>2.0430000000000001</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>2.464</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>2.7559999999999998</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="2">
         <v>2.36</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>1.758</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="2">
         <v>1.819</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>2.4</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="2">
         <v>2.4279999999999999</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="2">
         <v>2.15</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="2">
         <v>2.17</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="2">
         <v>1.9</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="2">
         <v>2.76</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="2">
         <v>2.4500000000000002</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="2">
         <v>2.12</v>
       </c>
-      <c r="U2" s="3">
+      <c r="U2" s="2">
         <v>1.9159999999999999</v>
       </c>
-      <c r="V2" s="3">
+      <c r="V2" s="2">
         <v>2.0419999999999998</v>
       </c>
-      <c r="W2" s="3">
+      <c r="W2" s="2">
         <v>2.0409999999999999</v>
       </c>
-      <c r="X2" s="3">
+      <c r="X2" s="2">
         <v>2.3420000000000001</v>
       </c>
-      <c r="Y2" s="3">
+      <c r="Y2" s="2">
         <v>2.7389999999999999</v>
       </c>
-      <c r="Z2" s="3">
+      <c r="Z2" s="2">
         <v>3.0859999999999999</v>
       </c>
-      <c r="AA2" s="3">
+      <c r="AA2" s="2">
         <v>3.4729999999999999</v>
       </c>
-      <c r="AB2" s="3">
+      <c r="AB2" s="2">
         <v>3.0590000000000002</v>
       </c>
-      <c r="AC2" s="3">
+      <c r="AC2" s="2">
         <v>2.4460000000000002</v>
       </c>
-      <c r="AD2" s="3" t="s">
+      <c r="AD2" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>1.66</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>3.25</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>2.9249999999999998</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>5.851</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="2">
         <v>5.8449999999999998</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="2">
         <v>4.8730000000000002</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="2">
         <v>2.234</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="2">
         <v>3.8250000000000002</v>
       </c>
-      <c r="L3" s="3">
+      <c r="L3" s="2">
         <v>5.88</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="2">
         <v>5.0259999999999998</v>
       </c>
-      <c r="N3" s="3">
+      <c r="N3" s="2">
         <v>5.9</v>
       </c>
-      <c r="O3" s="3">
+      <c r="O3" s="2">
         <v>5.8</v>
       </c>
-      <c r="P3" s="3">
+      <c r="P3" s="2">
         <v>4.38</v>
       </c>
-      <c r="Q3" s="3">
+      <c r="Q3" s="2">
         <v>5.53</v>
       </c>
-      <c r="R3" s="3">
+      <c r="R3" s="2">
         <v>6</v>
       </c>
-      <c r="S3" s="3">
+      <c r="S3" s="2">
         <v>5.54</v>
       </c>
-      <c r="T3" s="3">
+      <c r="T3" s="2">
         <v>6.73</v>
       </c>
-      <c r="U3" s="3">
+      <c r="U3" s="2">
         <v>4.2640000000000002</v>
       </c>
-      <c r="V3" s="3">
+      <c r="V3" s="2">
         <v>5.4279999999999999</v>
       </c>
-      <c r="W3" s="3">
+      <c r="W3" s="2">
         <v>5.1550000000000002</v>
       </c>
-      <c r="X3" s="3">
+      <c r="X3" s="2">
         <v>6.2350000000000003</v>
       </c>
-      <c r="Y3" s="3">
+      <c r="Y3" s="2">
         <v>7.6790000000000003</v>
       </c>
-      <c r="Z3" s="3">
+      <c r="Z3" s="2">
         <v>10.554</v>
       </c>
-      <c r="AA3" s="3">
+      <c r="AA3" s="2">
         <v>8.0969999999999995</v>
       </c>
-      <c r="AB3" s="3">
+      <c r="AB3" s="2">
         <v>7.8890000000000002</v>
       </c>
-      <c r="AC3" s="3">
+      <c r="AC3" s="2">
         <v>7.8730000000000002</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AD3" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
+      <c r="A4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>7.1890000000000001</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>6.7469999999999999</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>6.9729999999999999</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>5.359</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>5.2380000000000004</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="2">
         <v>6.609</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>8.0139999999999993</v>
       </c>
-      <c r="K4" s="3">
+      <c r="K4" s="2">
         <v>6.7729999999999997</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="2">
         <v>6.4109999999999996</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="2">
         <v>7.1580000000000004</v>
       </c>
-      <c r="N4" s="3">
+      <c r="N4" s="2">
         <v>6.6929999999999996</v>
       </c>
-      <c r="O4" s="3">
+      <c r="O4" s="2">
         <v>7.3380000000000001</v>
       </c>
-      <c r="P4" s="3">
+      <c r="P4" s="2">
         <v>7.3570000000000002</v>
       </c>
-      <c r="Q4" s="3">
+      <c r="Q4" s="2">
         <v>7.0659999999999998</v>
       </c>
-      <c r="R4" s="3">
+      <c r="R4" s="2">
         <v>5.3739999999999997</v>
       </c>
-      <c r="S4" s="3">
+      <c r="S4" s="2">
         <v>6.7450000000000001</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="2">
         <v>7.3490000000000002</v>
       </c>
-      <c r="U4" s="3">
+      <c r="U4" s="2">
         <v>7.0209999999999999</v>
       </c>
-      <c r="V4" s="3">
+      <c r="V4" s="2">
         <v>7.02</v>
       </c>
-      <c r="W4" s="3">
+      <c r="W4" s="2">
         <v>7.0289999999999999</v>
       </c>
-      <c r="X4" s="3">
+      <c r="X4" s="2">
         <v>6.3949999999999996</v>
       </c>
-      <c r="Y4" s="3">
+      <c r="Y4" s="2">
         <v>6.3920000000000003</v>
       </c>
-      <c r="Z4" s="3">
+      <c r="Z4" s="2">
         <v>4.6779999999999999</v>
       </c>
-      <c r="AA4" s="3">
+      <c r="AA4" s="2">
         <v>6.609</v>
       </c>
-      <c r="AB4" s="3">
+      <c r="AB4" s="2">
         <v>7.2009999999999996</v>
       </c>
-      <c r="AC4" s="3">
+      <c r="AC4" s="2">
         <v>6.8</v>
       </c>
-      <c r="AD4" s="3" t="s">
+      <c r="AD4" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="3" t="s">
+      <c r="A5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>3</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>5</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>5</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="2">
         <v>1.3779999999999999</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>15</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="2">
         <v>807</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>4</v>
       </c>
-      <c r="K5" s="3">
+      <c r="K5" s="2">
         <v>770</v>
       </c>
-      <c r="L5" s="3">
+      <c r="L5" s="2">
         <v>403</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="2">
         <v>1.1619999999999999</v>
       </c>
-      <c r="N5" s="3">
+      <c r="N5" s="2">
         <v>2.5350000000000001</v>
       </c>
-      <c r="O5" s="3">
+      <c r="O5" s="2">
         <v>2.036</v>
       </c>
-      <c r="P5" s="3">
+      <c r="P5" s="2">
         <v>1.5840000000000001</v>
       </c>
-      <c r="Q5" s="3">
+      <c r="Q5" s="2">
         <v>80</v>
       </c>
-      <c r="R5" s="3">
+      <c r="R5" s="2">
         <v>1.6910000000000001</v>
       </c>
-      <c r="S5" s="3">
+      <c r="S5" s="2">
         <v>1.0589999999999999</v>
       </c>
-      <c r="T5" s="3">
+      <c r="T5" s="2">
         <v>619</v>
       </c>
-      <c r="U5" s="3">
+      <c r="U5" s="2">
         <v>230</v>
       </c>
-      <c r="V5" s="3">
+      <c r="V5" s="2">
         <v>602</v>
       </c>
-      <c r="W5" s="3">
+      <c r="W5" s="2">
         <v>425</v>
       </c>
-      <c r="X5" s="3">
+      <c r="X5" s="2">
         <v>925</v>
       </c>
-      <c r="Y5" s="3">
+      <c r="Y5" s="2">
         <v>3.07</v>
       </c>
-      <c r="Z5" s="3">
+      <c r="Z5" s="2">
         <v>2.6869999999999998</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AA5" s="2">
         <v>2.8119999999999998</v>
       </c>
-      <c r="AB5" s="3">
+      <c r="AB5" s="2">
         <v>1.8939999999999999</v>
       </c>
-      <c r="AC5" s="3">
+      <c r="AC5" s="2">
         <v>2.1</v>
       </c>
-      <c r="AD5" s="3" t="s">
+      <c r="AD5" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>9.6</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>9.6999999999999993</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>9.85</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="2">
         <v>9.9</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="2">
         <v>10.199999999999999</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="2">
         <v>10.45</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>10.3</v>
       </c>
-      <c r="K6" s="3">
+      <c r="K6" s="2">
         <v>10.3</v>
       </c>
-      <c r="L6" s="3">
+      <c r="L6" s="2">
         <v>10.7</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="2">
         <v>11</v>
       </c>
-      <c r="N6" s="3">
+      <c r="N6" s="2">
         <v>10.8</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="2">
         <v>11.2</v>
       </c>
-      <c r="P6" s="3">
+      <c r="P6" s="2">
         <v>10.9</v>
       </c>
-      <c r="Q6" s="3">
+      <c r="Q6" s="2">
         <v>11.4</v>
       </c>
-      <c r="R6" s="3">
+      <c r="R6" s="2">
         <v>10.7</v>
       </c>
-      <c r="S6" s="3">
+      <c r="S6" s="2">
         <v>11.1</v>
       </c>
-      <c r="T6" s="3">
+      <c r="T6" s="2">
         <v>11.8</v>
       </c>
-      <c r="U6" s="3">
+      <c r="U6" s="2">
         <v>11.8</v>
       </c>
-      <c r="V6" s="3">
+      <c r="V6" s="2">
         <v>11.9</v>
       </c>
-      <c r="W6" s="3">
+      <c r="W6" s="2">
         <v>11.9</v>
       </c>
-      <c r="X6" s="3">
+      <c r="X6" s="2">
         <v>11.8</v>
       </c>
-      <c r="Y6" s="3">
+      <c r="Y6" s="2">
         <v>11.75</v>
       </c>
-      <c r="Z6" s="3">
+      <c r="Z6" s="2">
         <v>11.85</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="2">
         <v>12</v>
       </c>
-      <c r="AB6" s="3">
+      <c r="AB6" s="2">
         <v>12.2</v>
       </c>
-      <c r="AC6" s="3">
+      <c r="AC6" s="2">
         <v>12.35</v>
       </c>
-      <c r="AD6" s="3" t="s">
+      <c r="AD6" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>546</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>838</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <v>881</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="2">
         <v>813</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="2">
         <v>1.681</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="2">
         <v>1.9059999999999999</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="2">
         <v>1.85</v>
       </c>
-      <c r="K7" s="3">
+      <c r="K7" s="2">
         <v>1.3779999999999999</v>
       </c>
-      <c r="L7" s="3">
+      <c r="L7" s="2">
         <v>2.5659999999999998</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="2">
         <v>2.5880000000000001</v>
       </c>
-      <c r="N7" s="3">
+      <c r="N7" s="2">
         <v>1.8460000000000001</v>
       </c>
-      <c r="O7" s="3">
+      <c r="O7" s="2">
         <v>1.748</v>
       </c>
-      <c r="P7" s="3">
+      <c r="P7" s="2">
         <v>1.0009999999999999</v>
       </c>
-      <c r="Q7" s="3">
+      <c r="Q7" s="2">
         <v>2.117</v>
       </c>
-      <c r="R7" s="3">
+      <c r="R7" s="2">
         <v>1.1000000000000001</v>
       </c>
-      <c r="S7" s="3">
+      <c r="S7" s="2">
         <v>1.226</v>
       </c>
-      <c r="T7" s="3">
+      <c r="T7" s="2">
         <v>2.8860000000000001</v>
       </c>
-      <c r="U7" s="3">
+      <c r="U7" s="2">
         <v>2.141</v>
       </c>
-      <c r="V7" s="3">
+      <c r="V7" s="2">
         <v>2.0870000000000002</v>
       </c>
-      <c r="W7" s="3">
+      <c r="W7" s="2">
         <v>1.946</v>
       </c>
-      <c r="X7" s="3">
+      <c r="X7" s="2">
         <v>1.851</v>
       </c>
-      <c r="Y7" s="3">
+      <c r="Y7" s="2">
         <v>1.1020000000000001</v>
       </c>
-      <c r="Z7" s="3">
+      <c r="Z7" s="2">
         <v>1.7969999999999999</v>
       </c>
-      <c r="AA7" s="3">
+      <c r="AA7" s="2">
         <v>1.6910000000000001</v>
       </c>
-      <c r="AB7" s="3">
+      <c r="AB7" s="2">
         <v>2.6869999999999998</v>
       </c>
-      <c r="AC7" s="3">
+      <c r="AC7" s="2">
         <v>2.91</v>
       </c>
-      <c r="AD7" s="3" t="s">
+      <c r="AD7" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="3" t="s">
+      <c r="A8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="H8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="M8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="O8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="P8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="Q8" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="R8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="S8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="T8" s="3" t="s">
+      <c r="T8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="U8" s="3" t="s">
+      <c r="U8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="V8" s="3" t="s">
+      <c r="V8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="W8" s="3" t="s">
+      <c r="W8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="X8" s="3" t="s">
+      <c r="X8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="Y8" s="3" t="s">
+      <c r="Y8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="Z8" s="3" t="s">
+      <c r="Z8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AA8" s="3" t="s">
+      <c r="AA8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="AB8" s="3" t="s">
+      <c r="AB8" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="AC8" s="3" t="s">
+      <c r="AC8" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AD8" s="3" t="s">
+      <c r="AD8" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>215.18700000000001</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>214.18</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>212.68799999999999</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="2">
         <v>207.21799999999999</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>215.78899999999999</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="2">
         <v>217.44499999999999</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="2">
         <v>212.44399999999999</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="2">
         <v>217.02</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="2">
         <v>223.43299999999999</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="2">
         <v>225.75399999999999</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="2">
         <v>216.83799999999999</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="2">
         <v>220.91</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="2">
         <v>216.1</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="2">
         <v>219.78100000000001</v>
       </c>
-      <c r="R9" s="3">
+      <c r="R9" s="2">
         <v>221.40299999999999</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="2">
         <v>223.41200000000001</v>
       </c>
-      <c r="T9" s="3">
+      <c r="T9" s="2">
         <v>222.541</v>
       </c>
-      <c r="U9" s="3">
+      <c r="U9" s="2">
         <v>217.94499999999999</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="2">
         <v>214.697</v>
       </c>
-      <c r="W9" s="3">
+      <c r="W9" s="2">
         <v>215.24100000000001</v>
       </c>
-      <c r="X9" s="3">
+      <c r="X9" s="2">
         <v>220.21600000000001</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="2">
         <v>221.65100000000001</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="2">
         <v>219.66200000000001</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AA9" s="2">
         <v>222.251</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AB9" s="2">
         <v>222.26900000000001</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AC9" s="2">
         <v>220.054</v>
       </c>
-      <c r="AD9" s="3" t="s">
+      <c r="AD9" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="3" t="s">
+      <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>582.81299999999999</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>583.79100000000005</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>570.05799999999999</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="2">
         <v>556.08799999999997</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>627.06100000000004</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="2">
         <v>619.10500000000002</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="2">
         <v>596.83399999999995</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="2">
         <v>611.71</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="2">
         <v>684.26199999999994</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="2">
         <v>687.53099999999995</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="2">
         <v>650.29999999999995</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="2">
         <v>698.74300000000005</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="2">
         <v>660.81</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="2">
         <v>718.13199999999995</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="2">
         <v>732.11599999999999</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="2">
         <v>739.03599999999994</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="2">
         <v>757.26900000000001</v>
       </c>
-      <c r="U10" s="3">
+      <c r="U10" s="2">
         <v>760.30799999999999</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="2">
         <v>729.89300000000003</v>
       </c>
-      <c r="W10" s="3">
+      <c r="W10" s="2">
         <v>759.30799999999999</v>
       </c>
-      <c r="X10" s="3">
+      <c r="X10" s="2">
         <v>772.75900000000001</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="2">
         <v>780.82</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="2">
         <v>790.47500000000002</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AA10" s="2">
         <v>791.53099999999995</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AB10" s="2">
         <v>799.32799999999997</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AC10" s="2">
         <v>844.15200000000004</v>
       </c>
-      <c r="AD10" s="3" t="s">
+      <c r="AD10" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3" t="s">
+      <c r="A11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>99.343999999999994</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>106.23399999999999</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>103.712</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="2">
         <v>101.107</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>110.44</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="2">
         <v>111.572</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="2">
         <v>113.934</v>
       </c>
-      <c r="K11" s="3">
+      <c r="K11" s="2">
         <v>113.496</v>
       </c>
-      <c r="L11" s="3">
+      <c r="L11" s="2">
         <v>137.703</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="2">
         <v>133.60499999999999</v>
       </c>
-      <c r="N11" s="3">
+      <c r="N11" s="2">
         <v>131.94499999999999</v>
       </c>
-      <c r="O11" s="3">
+      <c r="O11" s="2">
         <v>150.239</v>
       </c>
-      <c r="P11" s="3">
+      <c r="P11" s="2">
         <v>143.166</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="Q11" s="2">
         <v>158.953</v>
       </c>
-      <c r="R11" s="3">
+      <c r="R11" s="2">
         <v>159.41</v>
       </c>
-      <c r="S11" s="3">
+      <c r="S11" s="2">
         <v>170.10599999999999</v>
       </c>
-      <c r="T11" s="3">
+      <c r="T11" s="2">
         <v>183.66</v>
       </c>
-      <c r="U11" s="3">
+      <c r="U11" s="2">
         <v>184.22499999999999</v>
       </c>
-      <c r="V11" s="3">
+      <c r="V11" s="2">
         <v>174.108</v>
       </c>
-      <c r="W11" s="3">
+      <c r="W11" s="2">
         <v>188.376</v>
       </c>
-      <c r="X11" s="3">
+      <c r="X11" s="2">
         <v>194.74100000000001</v>
       </c>
-      <c r="Y11" s="3">
+      <c r="Y11" s="2">
         <v>200.547</v>
       </c>
-      <c r="Z11" s="3">
+      <c r="Z11" s="2">
         <v>212.88900000000001</v>
       </c>
-      <c r="AA11" s="3">
+      <c r="AA11" s="2">
         <v>223.23400000000001</v>
       </c>
-      <c r="AB11" s="3">
+      <c r="AB11" s="2">
         <v>201.04499999999999</v>
       </c>
-      <c r="AC11" s="3">
+      <c r="AC11" s="2">
         <v>217.62200000000001</v>
       </c>
-      <c r="AD11" s="3" t="s">
+      <c r="AD11" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="3" t="s">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>101.19499999999999</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>105.783</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <v>105.34099999999999</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="2">
         <v>108.51900000000001</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="2">
         <v>111.081</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="2">
         <v>117.39400000000001</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="2">
         <v>111.559</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="2">
         <v>116.39</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="2">
         <v>144.12100000000001</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="2">
         <v>136.76400000000001</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="2">
         <v>133.04</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="2">
         <v>157.64400000000001</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="2">
         <v>136.148</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="2">
         <v>165.935</v>
       </c>
-      <c r="R12" s="3">
+      <c r="R12" s="2">
         <v>164.25299999999999</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="2">
         <v>172.97200000000001</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="2">
         <v>186.77799999999999</v>
       </c>
-      <c r="U12" s="3">
+      <c r="U12" s="2">
         <v>185.44900000000001</v>
       </c>
-      <c r="V12" s="3">
+      <c r="V12" s="2">
         <v>176.23699999999999</v>
       </c>
-      <c r="W12" s="3">
+      <c r="W12" s="2">
         <v>194.59200000000001</v>
       </c>
-      <c r="X12" s="3">
+      <c r="X12" s="2">
         <v>203.541</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="2">
         <v>203.72800000000001</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="2">
         <v>221.96899999999999</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AA12" s="2">
         <v>222.23</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AB12" s="2">
         <v>210.458</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AC12" s="2">
         <v>221.88200000000001</v>
       </c>
-      <c r="AD12" s="3" t="s">
+      <c r="AD12" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="3" t="s">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>583.91200000000003</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>586.78700000000003</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>602.18100000000004</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="2">
         <v>581.49099999999999</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="2">
         <v>605.69200000000001</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="2">
         <v>616.35299999999995</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="2">
         <v>619.09900000000005</v>
       </c>
-      <c r="K13" s="3">
+      <c r="K13" s="2">
         <v>614.37800000000004</v>
       </c>
-      <c r="L13" s="3">
+      <c r="L13" s="2">
         <v>636.77499999999998</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="2">
         <v>650.87199999999996</v>
       </c>
-      <c r="N13" s="3">
+      <c r="N13" s="2">
         <v>653.37300000000005</v>
       </c>
-      <c r="O13" s="3">
+      <c r="O13" s="2">
         <v>690.83399999999995</v>
       </c>
-      <c r="P13" s="3">
+      <c r="P13" s="2">
         <v>687.33900000000006</v>
       </c>
-      <c r="Q13" s="3">
+      <c r="Q13" s="2">
         <v>691.03700000000003</v>
       </c>
-      <c r="R13" s="3">
+      <c r="R13" s="2">
         <v>702.41600000000005</v>
       </c>
-      <c r="S13" s="3">
+      <c r="S13" s="2">
         <v>713.92899999999997</v>
       </c>
-      <c r="T13" s="3">
+      <c r="T13" s="2">
         <v>734.19299999999998</v>
       </c>
-      <c r="U13" s="3">
+      <c r="U13" s="2">
         <v>739.56600000000003</v>
       </c>
-      <c r="V13" s="3">
+      <c r="V13" s="2">
         <v>731.25400000000002</v>
       </c>
-      <c r="W13" s="3">
+      <c r="W13" s="2">
         <v>739.04200000000003</v>
       </c>
-      <c r="X13" s="3">
+      <c r="X13" s="2">
         <v>776.54300000000001</v>
       </c>
-      <c r="Y13" s="3">
+      <c r="Y13" s="2">
         <v>787.63900000000001</v>
       </c>
-      <c r="Z13" s="3">
+      <c r="Z13" s="2">
         <v>781.97900000000004</v>
       </c>
-      <c r="AA13" s="3">
+      <c r="AA13" s="2">
         <v>797.57899999999995</v>
       </c>
-      <c r="AB13" s="3">
+      <c r="AB13" s="2">
         <v>800.47</v>
       </c>
-      <c r="AC13" s="3">
+      <c r="AC13" s="2">
         <v>815.86199999999997</v>
       </c>
-      <c r="AD13" s="3" t="s">
+      <c r="AD13" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3" t="s">
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="2">
         <v>206.12200000000001</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>203.577</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>169.82499999999999</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="2">
         <v>137.01</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <v>157.738</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="2">
         <v>154.66800000000001</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="2">
         <v>134.77799999999999</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="2">
         <v>129.21600000000001</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="2">
         <v>170.285</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="2">
         <v>203.785</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="2">
         <v>199.61699999999999</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="2">
         <v>200.12100000000001</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="2">
         <v>180.61</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="2">
         <v>200.72300000000001</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="2">
         <v>225.58</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="2">
         <v>247.821</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="2">
         <v>267.779</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="2">
         <v>287.29700000000003</v>
       </c>
-      <c r="V14" s="3">
+      <c r="V14" s="2">
         <v>283.80700000000002</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="2">
         <v>297.85700000000003</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="2">
         <v>285.27300000000002</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="2">
         <v>275.27300000000002</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="2">
         <v>274.68900000000002</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="2">
         <v>269.64499999999998</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="2">
         <v>259.08999999999997</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="2">
         <v>283.12</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AD14" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3" t="s">
+      <c r="A15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="L15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="M15" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="N15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="O15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="P15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="Q15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="R15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="S15" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="T15" s="3" t="s">
+      <c r="T15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="U15" s="3" t="s">
+      <c r="U15" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="V15" s="3" t="s">
+      <c r="V15" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="W15" s="3" t="s">
+      <c r="W15" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="X15" s="3" t="s">
+      <c r="X15" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="Y15" s="3" t="s">
+      <c r="Y15" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="Z15" s="3" t="s">
+      <c r="Z15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AA15" s="3" t="s">
+      <c r="AA15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="AB15" s="3" t="s">
+      <c r="AB15" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="AC15" s="3" t="s">
+      <c r="AC15" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="AD15" s="3" t="s">
+      <c r="AD15" s="2" t="s">
         <v>65</v>
       </c>
     </row>
